--- a/pensum/ok01/OK01_Etablering_og_oppstart_Oppgaver_v6.xlsx
+++ b/pensum/ok01/OK01_Etablering_og_oppstart_Oppgaver_v6.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="143">
   <si>
     <t xml:space="preserve">Etablering og oppstart av egen bedrift: oppgaver til kapittel 1</t>
   </si>
@@ -65,10 +65,19 @@
     <t xml:space="preserve">Dette er øvingsmateriell til repetisjons- og øvingsstøtte. I besvarelser, caser, prosjektoppgaver og eksamen gjelder lærebøkene og oppgitte primærkilder.</t>
   </si>
   <si>
+    <t xml:space="preserve">700 000 kr, hennes halvdel</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1A: Nordlys i 2019: hvem betaler hvis det går galt?</t>
   </si>
   <si>
+    <t xml:space="preserve">1 400 000 kr, hele gjelden</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alene, i par eller i gruppe, slik du vil.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 kr, fordi selskapet er en egen enhet</t>
   </si>
   <si>
     <t xml:space="preserve">Situasjonen</t>
@@ -149,9 +158,15 @@
     <t xml:space="preserve">Gule celler fyller du inn. Grønne regnes ut av arket. Sjekken til høyre forteller om svaret stemmer, og hva du bør se på hvis ikke.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ja</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1B: Fjell Elektro: kan Mona starte, og hva må på plass?</t>
   </si>
   <si>
+    <t xml:space="preserve">Nei</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mona Fjell vil starte Fjell Elektro AS i Oslo med to montører, og selv være daglig leder og faglig ansvarlig og jobbe halve tiden ute på oppdrag. Før selskapsformen kommer retten til å tilby arbeidet: foretaket må stå i Elvirksomhetsregisteret med en faglig ansvarlig som fyller kravene i forskrift om elektroforetak og kvalifikasjonskrav. Så kommer registrene i Brønnøysund og hos Skatteetaten.</t>
   </si>
   <si>
@@ -170,13 +185,25 @@
     <t xml:space="preserve">År</t>
   </si>
   <si>
+    <t xml:space="preserve">Enhetsregisteret</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fagbrev som elektriker</t>
   </si>
   <si>
+    <t xml:space="preserve">Foretaksregisteret</t>
+  </si>
+  <si>
     <t xml:space="preserve">Montør fra 2012 til</t>
   </si>
   <si>
+    <t xml:space="preserve">Elvirksomhetsregisteret</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fagskoletekniker elkraft, ferdig i juni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merverdiavgiftsregisteret</t>
   </si>
   <si>
     <t xml:space="preserve">Prosjektleder i en installasjonsbedrift fra august</t>
@@ -236,7 +263,16 @@
     <t xml:space="preserve">e) Mona eier alene, og enkeltpersonforetak er enklere og billigere. Hvorfor bør Fjell Elektro likevel være aksjeselskap? Gi to argumenter (bruk ordene ansvar og trygd) og si hvorfor skatt ikke er argumentet.</t>
   </si>
   <si>
+    <t xml:space="preserve">15. februar og 15. april i år 2, i to like deler</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1C: Fjell Elektro år 1: skatt og merverdiavgift på kontoen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hver måned i år 1, sammen med lønna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15. mars, 15. juni, 15. september og 15. desember i år 1</t>
   </si>
   <si>
     <t xml:space="preserve">Fjell Elektro AS er i gang. Mona ser pengene komme inn på konto og vil vite hva som faktisk er bedriftens. Du skal lese fakturaen, innbetalingene og de to regningene til staten: merverdiavgiften annenhver måned og skatten året etter. Du skal ikke føre noe; du skal se hva kontoen egentlig viser.</t>
@@ -612,7 +648,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -635,6 +671,10 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1085,7 +1125,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G36"/>
+  <dimension ref="B1:Z36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1093,302 +1133,314 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="B9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>22</v>
+      <c r="B11" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="12" t="n">
+      <c r="B12" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="13" t="n">
         <v>300000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="12" t="n">
+      <c r="B13" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="13" t="n">
         <v>877500</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="12" t="n">
+      <c r="B14" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="13" t="n">
         <v>1400000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="12" t="n">
+      <c r="B15" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="13" t="n">
         <v>700000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="12" t="n">
+      <c r="B16" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="13" t="n">
         <v>700000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
+      <c r="B18" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
+      <c r="B19" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
     </row>
     <row r="21" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="14"/>
-      <c r="D21" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="G21" s="16" t="str">
+      <c r="B21" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="15"/>
+      <c r="D21" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G21" s="17" t="str">
         <f aca="false">IF(C21="","Skriv svaret i den gule cellen.",IF(C21=(300000),"Riktig.",IF(ABS(C21-(0))&lt;=0,"Du har svart 0. Aksjekapitalen på 300 000 er tapt; den var eiernes penger. Men etterpå skylder de ingenting.",IF(ABS(C21-(1400000))&lt;=0,"Du har svart den udekkede gjelden. I et aksjeselskap skylder eierne ikke den; ansvaret er begrenset til innskuddet.",IF(ABS(C21-(1700000))&lt;=0,"Du har lagt innskuddet til hele gjelden. Gjelden er selskapets, ikke eiernes. Bare innskuddet er tapt.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="G22" s="16" t="str">
+      <c r="B22" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="15"/>
+      <c r="D22" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G22" s="17" t="str">
         <f aca="false">IF(C22="","Skriv svaret i den gule cellen.",IF(C22=(700000),"Riktig.",IF(ABS(C22-(877500))&lt;=0,"Du har tatt hele lånet. Banken mangler bare 700 000 etter boet; kausjonen dekker det som mangler, ikke hele lånet.",IF(ABS(C22-(1400000))&lt;=0,"Du har tatt all udekket gjeld. Kausjonen gjelder bare banklånet. Polarlys har ingen kausjon og må bære sitt tap selv.",IF(ABS(C22-(300000))&lt;=0,"Det er aksjekapitalen, som er tapt uansett. Spørsmålet er hva banken kan kreve i tillegg.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="G23" s="16" t="str">
+      <c r="B23" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="15"/>
+      <c r="D23" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23" s="17" t="str">
         <f aca="false">IF(C23="","Skriv svaret i den gule cellen.",IF(C23=(300000+700000),"Riktig.",IF(ABS(C23-(700000))&lt;=0,"Det er bare det banken kan kreve. Aksjekapitalen på 300 000 er også tapt.",IF(ABS(C23-(300000))&lt;=0,"Det er bare aksjekapitalen. Legg til det banken kan kreve etter kausjonen.",IF(ABS(C23-(1700000))&lt;=0,"Du har lagt innskuddet til all udekket gjeld. Bare bankens del, 700 000, kan kreves av dem privat.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="15"/>
+      <c r="D24" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="14"/>
-      <c r="D24" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="G24" s="16" t="str">
+      <c r="G24" s="17" t="str">
         <f aca="false">IF(C24="","Skriv svaret i den gule cellen.",IF(C24=(1400000*0.5),"Riktig.",IF(ABS(C24-(1400000))&lt;=0,"Du har svart hele gjelden. Det er solidarisk ansvar (ANS). Ved delt ansvar svarer hver for sin andel.",IF(ABS(C24-(350000))&lt;=0,"Du har tatt halvparten av bare bankens del. Delt ansvar gjelder hele den udekkede gjelden, 1 400 000, delt etter eierandel.",IF(ABS(C24-(0))&lt;=0,"Du har svart 0. Det gjelder bare aksjeselskap. Et selskap med delt ansvar er et personlig selskap; eierne skylder det som mangler.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" s="17"/>
-      <c r="G25" s="16" t="str">
+      <c r="B25" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="18"/>
+      <c r="G25" s="17" t="str">
         <f aca="false">IF(C25="","Velg i nedtrekksmenyen.",IF(C25="1 400 000 kr, hele gjelden","Riktig. Solidarisk ansvar er én for alle og alle for én (boka 1.3): banken og Polarlys kan kreve hele beløpet av Kari, og så må hun kreve Tom for hans halvdel etterpå.","Ikke riktig. Solidarisk ansvar er én for alle og alle for én (boka 1.3): banken og Polarlys kan kreve hele beløpet av Kari, og så må hun kreve Tom for hans halvdel etterpå."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="G26" s="16" t="str">
+      <c r="B26" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="15"/>
+      <c r="D26" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G26" s="17" t="str">
         <f aca="false">IF(C26="","Skriv svaret i den gule cellen.",IF(C26=(1400000),"Riktig.",IF(ABS(C26-(700000))&lt;=0,"Du har delt på to. I et enkeltpersonforetak er det bare én eier, og hun skylder alt som mangler.",IF(ABS(C26-(0))&lt;=0,"Du har svart 0. Det gjelder bare aksjeselskap. I et enkeltpersonforetak er eier og foretak ett; gjelden er hennes.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
+      <c r="B28" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="19" t="str">
+      <c r="B32" s="20" t="str">
         <f aca="false">IF(LEN(B29)&lt;40,"",IF(AND(ISNUMBER(SEARCH("kausjon",B29)),ISNUMBER(SEARCH("Polarlys",B29))),"Bra: du ser at kausjonen bare gjelder banklånet, og at aksjeselskapet skjermer dem mot Polarlys og alle andre krav. Si også hva de bør be banken om: et tak i kroner og en dato kausjonen faller bort.",IF(OR(ISNUMBER(SEARCH("kausjon",B29)),ISNUMBER(SEARCH("Polarlys",B29))),"Du er på sporet. Ta med begge: at aksjeselskapet skjermer mot Polarlys og andre kreditorer, og at kausjonen bør forhandles (tak og sluttdato).","Tips: kausjonen gjelder bare banklånet. I et ansvarlig selskap kunne Polarlys gått etter Karis hus. Aksjeselskap skjermer mot alt annet enn kausjonen. Be banken om et tak i kroner og en dato kausjonen faller bort.")))</f>
         <v/>
       </c>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C33" s="17"/>
+      <c r="B33" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="18"/>
     </row>
     <row r="34" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="21" t="str">
+      <c r="B34" s="22" t="str">
         <f aca="false">IF(C33="JA","Hint: a: aksjekapitalen 300 000 er tapt, ingenting skyldes etterpå. b: banken mangler 700 000 og har kausjon, så den kan kreve 700 000 privat. c: 300 000 + 700 000 = 1 000 000. d: delt ansvar, 50 % av 1 400 000 = 700 000. e: solidarisk ansvar, hele 1 400 000 av hvem som helst av eierne. f: enkeltpersonforetak, hele 1 400 000.","")</f>
         <v/>
       </c>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="21"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
+      <c r="B36" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -1458,7 +1510,7 @@
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C25" type="list">
-      <formula1>"700 000 kr,hennes halvdel,1 400 000 kr,hele gjelden,0 kr,fordi selskapet er en egen enhet"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C33" type="list">
@@ -1481,7 +1533,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G46"/>
+  <dimension ref="B1:Z46"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1489,363 +1541,452 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="Z4" s="6" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="Z5" s="6" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="Z6" s="6" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="Z7" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="Z9" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="Z10" s="6" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>46</v>
+      <c r="B11" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z11" s="6" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="22" t="n">
+      <c r="B12" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="23" t="n">
         <v>2012</v>
       </c>
+      <c r="Z12" s="6" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="22" t="n">
+      <c r="B13" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="23" t="n">
         <v>2017</v>
       </c>
+      <c r="Z13" s="6" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" s="22" t="n">
+      <c r="B14" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="23" t="n">
         <v>2019</v>
       </c>
+      <c r="Z14" s="6" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="22" t="n">
+      <c r="B15" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="23" t="n">
         <v>2019</v>
       </c>
+      <c r="Z15" s="6" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="22" t="n">
+      <c r="B16" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="23" t="n">
         <v>2023</v>
       </c>
+      <c r="Z16" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z17" s="0" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
+      <c r="B18" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="Z18" s="6" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="Z19" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z20" s="0" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="23"/>
-      <c r="D21" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G21" s="16" t="str">
+      <c r="B21" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="24"/>
+      <c r="D21" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G21" s="17" t="str">
         <f aca="false">IF(C21="","Skriv svaret i den gule cellen.",IF(C21=(2023),"Riktig.",IF(ABS(C21-(2022))&lt;=0,"I august 2022 hadde hun tre års praksis etter utdanningen, men elektroinstallatørprøven var ikke bestått. Det siste vilkåret avgjør.",IF(ABS(C21-(2019))&lt;=0,"Da var hun ferdig på fagskolen, men praksisen etter utdanningen manglet. Montørårene før fagskolen teller ikke.",IF(ABS(C21-(2015))&lt;=0,"Du har regnet montørårene som praksis. Praksisen skal være opparbeidet etter endt utdanning (§ 7).",IF(ABS(C21-(2020))&lt;=0,"Du har regnet montørårene med. Praksisen teller først fra august 2019, og prøven kom i 2023.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z21" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z22" s="0" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
+      <c r="B23" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="Z23" s="6" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C24" s="17"/>
-      <c r="G24" s="16" t="str">
+      <c r="B24" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="18"/>
+      <c r="G24" s="17" t="str">
         <f aca="false">IF(C24="","Velg i nedtrekksmenyen.",IF(C24="Ja","Riktig. § 5: faglig ansvarlig skal være fast ansatt og tilgjengelig i foretakets normale arbeidstid. Å være ute på egne oppdrag er en del av jobben.","Ikke riktig. § 5: faglig ansvarlig skal være fast ansatt og tilgjengelig i foretakets normale arbeidstid. Å være ute på egne oppdrag er en del av jobben."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z24" s="6" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="17"/>
-      <c r="G25" s="16" t="str">
+      <c r="B25" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="18"/>
+      <c r="G25" s="17" t="str">
         <f aca="false">IF(C25="","Velg i nedtrekksmenyen.",IF(C25="Nei","Riktig. § 7: praksisen skal være opparbeidet etter endt utdanning. Montørarbeid gjenspeiler ikke den teoretiske utdanningen.","Ikke riktig. § 7: praksisen skal være opparbeidet etter endt utdanning. Montørarbeid gjenspeiler ikke den teoretiske utdanningen."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z25" s="6" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" s="17"/>
-      <c r="G26" s="16" t="str">
+      <c r="B26" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="G26" s="17" t="str">
         <f aca="false">IF(C26="","Velg i nedtrekksmenyen.",IF(C26="Nei","Riktig. § 3: plikten gjelder fra foretaket tilbyr arbeid. En annonse er å tilby.","Ikke riktig. § 3: plikten gjelder fra foretaket tilbyr arbeid. En annonse er å tilby."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z26" s="6" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C27" s="17"/>
-      <c r="G27" s="16" t="str">
+      <c r="B27" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" s="18"/>
+      <c r="G27" s="17" t="str">
         <f aca="false">IF(C27="","Velg i nedtrekksmenyen.",IF(C27="Nei","Riktig. § 5: faglig ansvarlig kan ikke ha en stilling med sammenfallende arbeidstid i et annet foretak.","Ikke riktig. § 5: faglig ansvarlig kan ikke ha en stilling med sammenfallende arbeidstid i et annet foretak."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="C28" s="17"/>
-      <c r="G28" s="16" t="str">
+      <c r="B28" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="G28" s="17" t="str">
         <f aca="false">IF(C28="","Velg i nedtrekksmenyen.",IF(C28="Nei","Riktig. Forskriften gjelder alle elektroforetak, uansett selskapsform. Selskapsformen avgjør ansvaret for gjelda, ikke retten til å tilby arbeidet.","Ikke riktig. Forskriften gjelder alle elektroforetak, uansett selskapsform. Selskapsformen avgjør ansvaret for gjelda, ikke retten til å tilby arbeidet."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" s="24"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="24"/>
+      <c r="B30" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C31" s="17"/>
-      <c r="G31" s="16" t="str">
+      <c r="B31" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="18"/>
+      <c r="G31" s="17" t="str">
         <f aca="false">IF(C31="","Velg i nedtrekksmenyen.",IF(C31="Enhetsregisteret","Riktig. Enhetsregisteret i Brønnøysund gir organisasjonsnummer til alle former. Et aksjeselskap registreres i Enhets- og Foretaksregisteret samtidig.","Ikke riktig. Enhetsregisteret i Brønnøysund gir organisasjonsnummer til alle former. Et aksjeselskap registreres i Enhets- og Foretaksregisteret samtidig."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="C32" s="17"/>
-      <c r="G32" s="16" t="str">
+      <c r="B32" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="18"/>
+      <c r="G32" s="17" t="str">
         <f aca="false">IF(C32="","Velg i nedtrekksmenyen.",IF(C32="Foretaksregisteret","Riktig. Foretaksregisteret er påbudt for aksjeselskap og ansvarlig selskap (boka 1.7). Attesten derfra gir tillit hos banker og leverandører.","Ikke riktig. Foretaksregisteret er påbudt for aksjeselskap og ansvarlig selskap (boka 1.7). Attesten derfra gir tillit hos banker og leverandører."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C33" s="17"/>
-      <c r="G33" s="16" t="str">
+      <c r="B33" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="18"/>
+      <c r="G33" s="17" t="str">
         <f aca="false">IF(C33="","Velg i nedtrekksmenyen.",IF(C33="Elvirksomhetsregisteret","Riktig. Elvirksomhetsregisteret hos Direktoratet for samfunnssikkerhet og beredskap (§ 3). Uten det kan foretaket ikke tilby elektroarbeid.","Ikke riktig. Elvirksomhetsregisteret hos Direktoratet for samfunnssikkerhet og beredskap (§ 3). Uten det kan foretaket ikke tilby elektroarbeid."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C34" s="17"/>
-      <c r="G34" s="16" t="str">
+      <c r="B34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" s="18"/>
+      <c r="G34" s="17" t="str">
         <f aca="false">IF(C34="","Velg i nedtrekksmenyen.",IF(C34="Merverdiavgiftsregisteret","Riktig. Merverdiavgiftsregisteret hos Skatteetaten. Grensen er 50 000 kr i avgiftspliktig omsetning på tolv måneder (merverdiavgiftsloven § 2-1).","Ikke riktig. Merverdiavgiftsregisteret hos Skatteetaten. Grensen er 50 000 kr i avgiftspliktig omsetning på tolv måneder (merverdiavgiftsloven § 2-1)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="C36" s="14"/>
-      <c r="D36" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="G36" s="16" t="str">
+      <c r="B36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C36" s="15"/>
+      <c r="D36" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G36" s="17" t="str">
         <f aca="false">IF(C36="","Skriv svaret i den gule cellen.",IF(C36=(6825),"Riktig.",IF(ABS(C36-(3883))&lt;=0,"Det er satsen for ansvarlig selskap, eller enkeltpersonforetak som også vil inn i Foretaksregisteret.",IF(ABS(C36-(2181))&lt;=0,"Det er enkeltpersonforetak i Enhetsregisteret alene. Et aksjeselskap må inn i Foretaksregisteret.",IF(ABS(C36-(7912))&lt;=0,"Det er satsen på papir. Elektronisk registrering er billigere.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
+      <c r="B38" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="18"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="18"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="18"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="19"/>
     </row>
     <row r="42" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="19" t="str">
+      <c r="B42" s="20" t="str">
         <f aca="false">IF(LEN(B39)&lt;40,"",IF(AND(ISNUMBER(SEARCH("ansvar",B39)),ISNUMBER(SEARCH("trygd",B39)),ISNUMBER(SEARCH("skatt",B39))),"Bra: du har ansvaret, trygderettighetene og poenget om at skatten ikke avgjør. Ansatte, kreditt hos grossisten og arbeid på andres anlegg gir risiko langt over innskuddet.",IF(OR(ISNUMBER(SEARCH("ansvar",B39)),ISNUMBER(SEARCH("trygd",B39)),ISNUMBER(SEARCH("skatt",B39))),"Du har noe av det. Ta med alle tre: ansvaret (hva hun kan tape privat), trygderettighetene som arbeidende aksjonær, og hvorfor 22 % i selskapet ikke kan sammenliknes med personskatt.","Tips: i aksjeselskap taper hun innskuddet og det hun har kausjonert for; i enkeltpersonforetak alt hun eier. Som arbeidende aksjonær har hun trygderettigheter som en ansatt. Skatten på 22 % er selskapets, og uttak skattes igjen, så den er ikke argumentet.")))</f>
         <v/>
       </c>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C43" s="17"/>
+      <c r="B43" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" s="18"/>
     </row>
     <row r="44" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="21" t="str">
+      <c r="B44" s="22" t="str">
         <f aca="false">IF(C43="JA","Hint: a: utdanning ferdig juni 2019, tre års praksis fra august 2019 gir august 2022, prøven 2023. Siste vilkår avgjør: 2023. b: bare den første påstanden er i orden. c: organisasjonsnummer i Enhetsregisteret, attest i Foretaksregisteret, faglig ansvarlig i Elvirksomhetsregisteret, merverdiavgift i Merverdiavgiftsregisteret. d: 6 825 kr for aksjeselskap elektronisk (brreg.no 2026).","")</f>
         <v/>
       </c>
-      <c r="C44" s="21"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="21"/>
-      <c r="G44" s="21"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="22"/>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
+      <c r="B46" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -1957,39 +2098,39 @@
   </conditionalFormatting>
   <dataValidations count="10">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C24" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$1:$Z$2</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C25" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$3:$Z$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C26" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$5:$Z$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C27" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$7:$Z$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C28" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$9:$Z$10</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C31" type="list">
-      <formula1>"Enhetsregisteret,Foretaksregisteret,Elvirksomhetsregisteret,Merverdiavgiftsregisteret"</formula1>
+      <formula1>$Z$11:$Z$14</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C32" type="list">
-      <formula1>"Enhetsregisteret,Foretaksregisteret,Elvirksomhetsregisteret,Merverdiavgiftsregisteret"</formula1>
+      <formula1>$Z$15:$Z$18</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C33" type="list">
-      <formula1>"Enhetsregisteret,Foretaksregisteret,Elvirksomhetsregisteret,Merverdiavgiftsregisteret"</formula1>
+      <formula1>$Z$19:$Z$22</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C34" type="list">
-      <formula1>"Enhetsregisteret,Foretaksregisteret,Elvirksomhetsregisteret,Merverdiavgiftsregisteret"</formula1>
+      <formula1>$Z$23:$Z$26</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C43" type="list">
@@ -2012,7 +2153,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G37"/>
+  <dimension ref="B1:Z37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2020,300 +2161,312 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>77</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="B9" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>22</v>
+      <c r="B11" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" s="12" t="n">
+      <c r="B12" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="13" t="n">
         <v>12460</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" s="12" t="n">
+      <c r="B13" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" s="13" t="n">
         <v>11760</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" s="25" t="n">
+      <c r="B14" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="26" t="n">
         <f aca="false">C12+C13</f>
         <v>24220</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
+      <c r="B16" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
+      <c r="B17" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
     </row>
     <row r="19" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="G19" s="16" t="str">
+      <c r="B19" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="15"/>
+      <c r="D19" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G19" s="17" t="str">
         <f aca="false">IF(C19="","Skriv svaret i den gule cellen.",IF(C19=(ROUND(24220*0.25,0)),"Riktig.",IF(ABS(C19-(ROUND(24220*0.2,0)))&lt;=0,"Du har regnet 20 % av beløpet uten avgift. Satsen er 25 % av beløpet uten avgift; 20 % gjelder bare når du regner bakover fra beløpet med avgift.",IF(ABS(C19-(ROUND(12460*0.25,0)))&lt;=0,"Du har regnet avgift bare på timene. Det er avgift på materiellet også.",IF(ABS(C19-(ROUND(24220/1.25,0)))&lt;=0,"Du har delt på 1,25. Det gir beløpet uten avgift når du starter med beløpet med avgift. Her skal du gange med 0,25.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="C20" s="14"/>
-      <c r="D20" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="G20" s="16" t="str">
+      <c r="B20" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" s="15"/>
+      <c r="D20" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" s="17" t="str">
         <f aca="false">IF(C20="","Skriv svaret i den gule cellen.",IF(C20=(ROUND(24220*1.25,0)),"Riktig.",IF(ABS(C20-(24220))&lt;=0,"Det er summen uten avgift. Kunden betaler summen pluss 25 %.",IF(ABS(C20-(ROUND(12460*1.25+11760,0)))&lt;=0,"Du har lagt avgift bare på timene. Materiellet har også 25 %.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="G22" s="16" t="str">
+      <c r="B22" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" s="15"/>
+      <c r="D22" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G22" s="17" t="str">
         <f aca="false">IF(C22="","Skriv svaret i den gule cellen.",IF(C22=(350000*1.25),"Riktig.",IF(ABS(C22-(350000))&lt;=0,"Kundene betaler beløpet med avgift. Legg til 25 %.",IF(ABS(C22-(ROUND(350000*0.25,0)))&lt;=0,"Det er bare avgiften. Hele fakturabeløpet med avgift kommer inn.",IF(ABS(C22-(400000*1.25))&lt;=0,"Du har tatt februarsalget. Med 30 dagers kreditt er det januarsalget som betales i februar.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="G23" s="16" t="str">
+      <c r="B23" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" s="15"/>
+      <c r="D23" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23" s="17" t="str">
         <f aca="false">IF(C23="","Skriv svaret i den gule cellen.",IF(C23=(350000*0.25),"Riktig.",IF(ABS(C23-(ROUND(437500*0.25,0)))&lt;=0,"Du har regnet 25 % av beløpet med avgift. Avgiften er 25 % av beløpet uten, altså 437 500 / 1,25 × 0,25, eller 20 % av beløpet med avgift.",IF(ABS(C23-(437500))&lt;=0,"Det er hele innbetalingen. Bare avgiftsdelen er statens.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="C25" s="14"/>
-      <c r="D25" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="G25" s="16" t="str">
+      <c r="B25" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" s="15"/>
+      <c r="D25" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G25" s="17" t="str">
         <f aca="false">IF(C25="","Skriv svaret i den gule cellen.",IF(C25=(750000*0.25-(240000+300000)*0.25),"Riktig.",IF(ABS(C25-(750000*0.25))&lt;=0,"Du har glemt den inngående avgiften. Avgiften Fjell har betalt på innkjøp og utstyr, trekkes fra.",IF(ABS(C25-(750000*0.25-240000*0.25))&lt;=0,"Du har glemt utstyret. Avgiften på de 300 000 i verktøy og utstyr er også inngående avgift og trekkes fra.",IF(ABS(C25-((240000+300000)*0.25-750000*0.25))&lt;=0,"Du har snudd fortegnet. Utgående avgift på salget er større enn inngående, så Fjell skal betale, ikke få tilbake.",IF(ABS(C25-((240000+300000)*0.25))&lt;=0,"Det er bare den inngående avgiften. Trekk den fra den utgående på salget.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="G26" s="16" t="str">
+      <c r="B26" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" s="15"/>
+      <c r="D26" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G26" s="17" t="str">
         <f aca="false">IF(C26="","Skriv svaret i den gule cellen.",IF(ABS(C26-(ROUND(106740*0.22,0)))&lt;=1,"Riktig.",IF(ABS(C26-(ROUND(106740*0.3,0)))&lt;=1,"Du har brukt 30 %. Det er personskatt i et enkeltpersonforetak. Fjell er et aksjeselskap: 22 % i selskapet.",IF(ABS(C26-(ROUND(144240*0.22,0)))&lt;=1,"Du har regnet av driftsresultatet. Skatten regnes av resultat før skatt, etter rentene: 106 740.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C27" s="17"/>
-      <c r="G27" s="16" t="str">
+      <c r="B27" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" s="18"/>
+      <c r="G27" s="17" t="str">
         <f aca="false">IF(C27="","Velg i nedtrekksmenyen.",IF(C27="15. februar og 15. april i år 2, i to like deler","Riktig. Et aksjeselskap betaler skatten etterskuddsvis (boka 1.4): forskuddsskatten forfaller 15. februar og 15. april året etter inntektsåret (Skatteetaten). De fire terminene i inntektsåret gjelder enkeltpersonforetak.","Ikke riktig. Et aksjeselskap betaler skatten etterskuddsvis (boka 1.4): forskuddsskatten forfaller 15. februar og 15. april året etter inntektsåret (Skatteetaten). De fire terminene i inntektsåret gjelder enkeltpersonforetak."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
+      <c r="B29" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
     </row>
     <row r="33" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="19" t="str">
+      <c r="B33" s="20" t="str">
         <f aca="false">IF(LEN(B30)&lt;40,"",IF(AND(ISNUMBER(SEARCH("merverdiavgift",B30)),ISNUMBER(SEARCH("skatt",B30))),"Bra: du skiller det som er Fjells fra det som er statens, og du har med at merverdiavgiften forfaller 10. april og skatten året etter. Det er å lese kontoen med kalenderen i hånda.",IF(OR(ISNUMBER(SEARCH("merverdiavgift",B30)),ISNUMBER(SEARCH("skatt",B30))),"Du er på sporet. Ta med begge: 87 500 av de 437 500 er merverdiavgift som skal betales 10. april, og skatten for år 1 forfaller 15. februar og 15. april i år 2.","Tips: 87 500 av de 437 500 er merverdiavgift, ikke Fjells penger; oppgjøret for januar og februar forfaller 10. april. Skatten på 23 483 for år 1 forfaller 15. februar og 15. april i år 2. Kontoen ser bedre ut enn den er.")))</f>
         <v/>
       </c>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C34" s="17"/>
+      <c r="B34" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" s="18"/>
     </row>
     <row r="35" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="21" t="str">
+      <c r="B35" s="22" t="str">
         <f aca="false">IF(C34="JA","Hint: a: 24 220 × 0,25 = 6 055. b: 24 220 × 1,25 = 30 275. c: 350 000 × 1,25 = 437 500. d: 350 000 × 0,25 = 87 500. e: 750 000 × 0,25 = 187 500 utgående, (240 000 + 300 000) × 0,25 = 135 000 inngående, 187 500 − 135 000 = 52 500. f: 106 740 × 0,22 = 23 483. g: 15. februar og 15. april i år 2.","")</f>
         <v/>
       </c>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
+      <c r="B37" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -2391,7 +2544,7 @@
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C27" type="list">
-      <formula1>"15. februar og 15. april i år 2,i to like deler,Hver måned i år 1,sammen med lønna,15. mars,15. juni,15. september og 15. desember i år 1"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C34" type="list">
@@ -2424,230 +2577,230 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="26" t="s">
-        <v>86</v>
+      <c r="B2" s="27" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>90</v>
+      <c r="B5" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="C6" s="25" t="n">
+      <c r="B6" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="26" t="n">
         <v>300000</v>
       </c>
-      <c r="D6" s="28" t="s">
-        <v>92</v>
+      <c r="D6" s="29" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="C7" s="25" t="n">
+      <c r="B7" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="26" t="n">
         <v>700000</v>
       </c>
-      <c r="D7" s="28" t="s">
-        <v>94</v>
+      <c r="D7" s="29" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="C8" s="25" t="n">
+      <c r="B8" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" s="26" t="n">
         <v>1000000</v>
       </c>
-      <c r="D8" s="28" t="s">
-        <v>96</v>
+      <c r="D8" s="29" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9" s="25" t="n">
+      <c r="B9" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" s="26" t="n">
         <v>700000</v>
       </c>
-      <c r="D9" s="28" t="s">
-        <v>98</v>
+      <c r="D9" s="29" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" s="25"/>
-      <c r="D10" s="28" t="s">
-        <v>100</v>
+      <c r="B10" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="26"/>
+      <c r="D10" s="29" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="28" t="s">
-        <v>101</v>
-      </c>
-      <c r="C11" s="25" t="n">
+      <c r="B11" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11" s="26" t="n">
         <v>1400000</v>
       </c>
-      <c r="D11" s="28" t="s">
-        <v>102</v>
+      <c r="D11" s="29" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="28" t="s">
-        <v>104</v>
+      <c r="B12" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" s="26"/>
+      <c r="D12" s="29" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="28" t="s">
-        <v>105</v>
-      </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="28" t="s">
-        <v>106</v>
+      <c r="B13" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="C13" s="26"/>
+      <c r="D13" s="29" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="C14" s="25"/>
-      <c r="D14" s="28" t="s">
-        <v>108</v>
+      <c r="B14" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="26"/>
+      <c r="D14" s="29" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="C15" s="25"/>
-      <c r="D15" s="28" t="s">
-        <v>110</v>
+      <c r="B15" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="C15" s="26"/>
+      <c r="D15" s="29" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="C16" s="25" t="n">
+      <c r="B16" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="C16" s="26" t="n">
         <v>6825</v>
       </c>
-      <c r="D16" s="28" t="s">
-        <v>112</v>
+      <c r="D16" s="29" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="28" t="s">
-        <v>113</v>
-      </c>
-      <c r="C17" s="25"/>
-      <c r="D17" s="28" t="s">
-        <v>114</v>
+      <c r="B17" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="26"/>
+      <c r="D17" s="29" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="C18" s="25" t="n">
+      <c r="B18" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="C18" s="26" t="n">
         <v>6055</v>
       </c>
-      <c r="D18" s="28" t="s">
-        <v>116</v>
+      <c r="D18" s="29" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="28" t="s">
-        <v>117</v>
-      </c>
-      <c r="C19" s="25" t="n">
+      <c r="B19" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" s="26" t="n">
         <v>30275</v>
       </c>
-      <c r="D19" s="28" t="s">
-        <v>118</v>
+      <c r="D19" s="29" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="C20" s="25" t="n">
+      <c r="B20" s="29" t="s">
+        <v>131</v>
+      </c>
+      <c r="C20" s="26" t="n">
         <v>437500</v>
       </c>
-      <c r="D20" s="28" t="s">
-        <v>120</v>
+      <c r="D20" s="29" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="C21" s="25" t="n">
+      <c r="B21" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="26" t="n">
         <v>87500</v>
       </c>
-      <c r="D21" s="28" t="s">
-        <v>122</v>
+      <c r="D21" s="29" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="C22" s="25" t="n">
+      <c r="B22" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="C22" s="26" t="n">
         <v>52500</v>
       </c>
-      <c r="D22" s="28" t="s">
-        <v>124</v>
+      <c r="D22" s="29" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="C23" s="25" t="n">
+      <c r="B23" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="26" t="n">
         <v>23483</v>
       </c>
-      <c r="D23" s="28" t="s">
-        <v>126</v>
+      <c r="D23" s="29" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="C24" s="25"/>
-      <c r="D24" s="28" t="s">
-        <v>128</v>
+      <c r="B24" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="C24" s="26"/>
+      <c r="D24" s="29" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="C25" s="25"/>
-      <c r="D25" s="28" t="s">
-        <v>130</v>
+      <c r="B25" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="C25" s="26"/>
+      <c r="D25" s="29" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/pensum/ok01/OK01_Etablering_og_oppstart_Oppgaver_v6.xlsx
+++ b/pensum/ok01/OK01_Etablering_og_oppstart_Oppgaver_v6.xlsx
@@ -83,13 +83,13 @@
     <t xml:space="preserve">Situasjonen</t>
   </si>
   <si>
-    <t xml:space="preserve">Det er 2019. Kari Nordlund (elektroinstallatør) og Tom Berg (elektriker) starter Nordlys Elektro AS og eier halvparten hver. De skyter inn 300 000 kr i aksjekapital. Banken låner dem 877 500 kr, men krever personlig kausjon fra begge. Tenk deg nå at første driftsår går galt og Nordlys går konkurs. Når boet er gjort opp, står det igjen 1 400 000 kr i udekket gjeld: 700 000 til banken og 700 000 til grossisten Polarlys. Regn hva Kari og Tom sitter igjen med i hver selskapsform.</t>
+    <t xml:space="preserve">Det er 2019. Kari Nordlund (elektroinstallatør) og Tom Berg (elektriker) starter Nordlys Elektro AS og eier halvparten hver. De skyter inn 675 000 kr: 300 000 kr i aksjekapital og 375 000 kr i overkurs. Banken låner dem 765 000 kr, men krever personlig kausjon fra begge. Tenk deg nå at første driftsår går galt og Nordlys går konkurs. Når boet er gjort opp, står det igjen 1 400 000 kr i udekket gjeld: 700 000 til banken og 700 000 til grossisten Polarlys. Regn hva Kari og Tom sitter igjen med i hver selskapsform.</t>
   </si>
   <si>
     <t xml:space="preserve">Begrepene du trenger</t>
   </si>
   <si>
-    <t xml:space="preserve">Personlig selskap (enkeltpersonforetak, ansvarlig selskap med solidarisk ansvar (ANS), selskap med delt ansvar (DA)): ingen vegg mellom eier og foretak; eierne skylder det som mangler etter konkursen. Aksjeselskap: eierne taper innskuddet, aksjekapitalen, men ikke mer. Personlig kausjon: et eget løfte til banken om å betale selv hvis selskapet ikke kan; gjelder bare det lånet, uansett selskapsform.</t>
+    <t xml:space="preserve">Personlig selskap (enkeltpersonforetak, ansvarlig selskap med solidarisk ansvar (ANS), selskap med delt ansvar (DA)): ingen vegg mellom eier og foretak; eierne skylder det som mangler etter konkursen. Aksjeselskap: eierne taper innskuddet (aksjekapital og overkurs), men ikke mer. Personlig kausjon: et eget løfte til banken om å betale selv hvis selskapet ikke kan; gjelder bare det lånet, uansett selskapsform.</t>
   </si>
   <si>
     <t xml:space="preserve">Tallene, i kroner</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">Kroner</t>
   </si>
   <si>
-    <t xml:space="preserve">Aksjekapital Kari og Tom skjøt inn i 2019</t>
+    <t xml:space="preserve">Innskutt egenkapital 2019: aksjekapital 300 000 + overkurs 375 000</t>
   </si>
   <si>
     <t xml:space="preserve">Banklån ved oppstart, personlig kausjon fra begge</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">Oppgaven, trinn for trinn</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Aksjeselskap uten kausjon (a): hva er tapt privat? Tenk på innskuddet, og på om eierne skylder noe etterpå.
+    <t xml:space="preserve">1. Aksjeselskap uten kausjon (a): hva er tapt privat? Tenk på innskuddet (aksjekapital og overkurs), og på om eierne skylder noe etterpå.
 2. Aksjeselskap med kausjonen banken krevde (b og c): hva kan banken kreve av Kari og Tom privat, og hva blir samlet tap? Polarlys har ingen kausjon.
 3. Tenk deg at de hadde valgt selskap med delt ansvar (DA), 50 % hver (d), ansvarlig selskap med solidarisk ansvar (ANS) (e), eller at Kari hadde startet alene som enkeltpersonforetak (f).
 4. Skriv svaret til Kari i g.</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">Mona Fjell vil starte Fjell Elektro AS i Oslo med to montører, og selv være daglig leder og faglig ansvarlig og jobbe halve tiden ute på oppdrag. Før selskapsformen kommer retten til å tilby arbeidet: foretaket må stå i Elvirksomhetsregisteret med en faglig ansvarlig som fyller kravene i forskrift om elektroforetak og kvalifikasjonskrav. Så kommer registrene i Brønnøysund og hos Skatteetaten.</t>
   </si>
   <si>
-    <t xml:space="preserve">Forskrift om elektroforetak og kvalifikasjonskrav: § 3 registrering i Elvirksomhetsregisteret før foretaket tilbyr arbeid; § 5 faglig ansvarlig er fast ansatt og tilgjengelig i normal arbeidstid; § 7 relevant utdanning, minst tre års relevant praksis etter endt utdanning, og bestått elektroinstallatørprøve for arbeid på andres anlegg. Enhetsregisteret gir organisasjonsnummer; Foretaksregisteret gir firmaattest og beskyttet navn; Merverdiavgiftsregisteret fra 50 000 kr i omsetning.</t>
+    <t xml:space="preserve">Forskrift om elektroforetak og kvalifikasjonskrav: registrering i Elvirksomhetsregisteret før foretaket tilbyr arbeid; faglig ansvarlig er fast ansatt og tilgjengelig i normal arbeidstid; § 7 relevant utdanning, minst tre års relevant praksis etter endt utdanning, og bestått elektroinstallatørprøve for arbeid på andres anlegg. Enhetsregisteret gir organisasjonsnummer; Foretaksregisteret gir firmaattest og beskyttet navn; Merverdiavgiftsregisteret fra 50 000 kr i omsetning.</t>
   </si>
   <si>
     <t xml:space="preserve">Monas vei, årstall</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">1A a) Aksjeselskap uten kausjon</t>
   </si>
   <si>
-    <t xml:space="preserve">Aksjekapitalen 300 000 kr er tapt. Etterpå skylder de ingenting (boka 1.4 og 1.6)</t>
+    <t xml:space="preserve">Innskuddet 675 000 kr (aksjekapital 300 000 + overkurs 375 000) er tapt. Etterpå skylder de ingenting (boka 1.4 og 1.6)</t>
   </si>
   <si>
     <t xml:space="preserve">1A b) Banken kan kreve etter kausjonen</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">1A c) Samlet tap med kausjon</t>
   </si>
   <si>
-    <t xml:space="preserve">300 000 + 700 000 = 1 000 000 kr. Polarlys bærer sine 700 000 selv</t>
+    <t xml:space="preserve">675 000 + 700 000 = 1 375 000 kr. Polarlys bærer sine 700 000 selv</t>
   </si>
   <si>
     <t xml:space="preserve">1A d) Delt ansvar (DA), Karis del</t>
@@ -395,7 +395,7 @@
     <t xml:space="preserve">1B b) Fem påstander</t>
   </si>
   <si>
-    <t xml:space="preserve">Bare den første er i orden (§ 5). Montørår teller ikke (§ 7), annonse før registrering er å tilby (§ 3), ikke delt stilling (§ 5), og kravet gjelder uansett selskapsform</t>
+    <t xml:space="preserve">Bare den første er i orden. Montørår teller ikke (§ 7), annonse før registrering i Elvirksomhetsregisteret er å tilby, ikke delt stilling, og kravet gjelder uansett selskapsform</t>
   </si>
   <si>
     <t xml:space="preserve">1B c) Registrene</t>
@@ -1240,7 +1240,7 @@
         <v>26</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>300000</v>
+        <v>675000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1248,7 +1248,7 @@
         <v>27</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>877500</v>
+        <v>765000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1285,7 +1285,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
     </row>
-    <row r="19" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="9" t="s">
         <v>32</v>
       </c>
@@ -1304,7 +1304,7 @@
         <v>34</v>
       </c>
       <c r="G21" s="17" t="str">
-        <f aca="false">IF(C21="","Skriv svaret i den gule cellen.",IF(C21=(300000),"Riktig.",IF(ABS(C21-(0))&lt;=0,"Du har svart 0. Aksjekapitalen på 300 000 er tapt; den var eiernes penger. Men etterpå skylder de ingenting.",IF(ABS(C21-(1400000))&lt;=0,"Du har svart den udekkede gjelden. I et aksjeselskap skylder eierne ikke den; ansvaret er begrenset til innskuddet.",IF(ABS(C21-(1700000))&lt;=0,"Du har lagt innskuddet til hele gjelden. Gjelden er selskapets, ikke eiernes. Bare innskuddet er tapt.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
+        <f aca="false">IF(C21="","Skriv svaret i den gule cellen.",IF(C21=(675000),"Riktig.",IF(ABS(C21-(0))&lt;=0,"Du har svart 0. Innskuddet på 675 000 er tapt; det var eiernes penger. Men etterpå skylder de ingenting.",IF(ABS(C21-(300000))&lt;=0,"Du har tatt bare aksjekapitalen. Overkursen på 375 000 betalte Kari og Tom også inn for aksjene, og den er like tapt.",IF(ABS(C21-(1400000))&lt;=0,"Du har svart den udekkede gjelden. I et aksjeselskap skylder eierne ikke den; ansvaret er begrenset til innskuddet.",IF(ABS(C21-(2075000))&lt;=0,"Du har lagt innskuddet til hele gjelden. Gjelden er selskapets, ikke eiernes. Bare innskuddet er tapt.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
         <v>34</v>
       </c>
       <c r="G22" s="17" t="str">
-        <f aca="false">IF(C22="","Skriv svaret i den gule cellen.",IF(C22=(700000),"Riktig.",IF(ABS(C22-(877500))&lt;=0,"Du har tatt hele lånet. Banken mangler bare 700 000 etter boet; kausjonen dekker det som mangler, ikke hele lånet.",IF(ABS(C22-(1400000))&lt;=0,"Du har tatt all udekket gjeld. Kausjonen gjelder bare banklånet. Polarlys har ingen kausjon og må bære sitt tap selv.",IF(ABS(C22-(300000))&lt;=0,"Det er aksjekapitalen, som er tapt uansett. Spørsmålet er hva banken kan kreve i tillegg.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
+        <f aca="false">IF(C22="","Skriv svaret i den gule cellen.",IF(C22=(700000),"Riktig.",IF(ABS(C22-(765000))&lt;=0,"Du har tatt hele lånet. Banken mangler bare 700 000 etter boet; kausjonen dekker det som mangler, ikke hele lånet.",IF(ABS(C22-(1400000))&lt;=0,"Du har tatt all udekket gjeld. Kausjonen gjelder bare banklånet. Polarlys har ingen kausjon og må bære sitt tap selv.",IF(ABS(C22-(675000))&lt;=0,"Det er innskuddet, som er tapt uansett. Spørsmålet er hva banken kan kreve i tillegg.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
         <v>34</v>
       </c>
       <c r="G23" s="17" t="str">
-        <f aca="false">IF(C23="","Skriv svaret i den gule cellen.",IF(C23=(300000+700000),"Riktig.",IF(ABS(C23-(700000))&lt;=0,"Det er bare det banken kan kreve. Aksjekapitalen på 300 000 er også tapt.",IF(ABS(C23-(300000))&lt;=0,"Det er bare aksjekapitalen. Legg til det banken kan kreve etter kausjonen.",IF(ABS(C23-(1700000))&lt;=0,"Du har lagt innskuddet til all udekket gjeld. Bare bankens del, 700 000, kan kreves av dem privat.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
+        <f aca="false">IF(C23="","Skriv svaret i den gule cellen.",IF(C23=(675000+700000),"Riktig.",IF(ABS(C23-(700000))&lt;=0,"Det er bare det banken kan kreve. Innskuddet på 675 000 er også tapt.",IF(ABS(C23-(675000))&lt;=0,"Det er bare innskuddet. Legg til det banken kan kreve etter kausjonen.",IF(ABS(C23-(1000000))&lt;=0,"Du har tatt med bare aksjekapitalen på 300 000. Overkursen på 375 000 er også innskutt og tapt: 675 000 + 700 000.",IF(ABS(C23-(2075000))&lt;=0,"Du har lagt innskuddet til all udekket gjeld. Bare bankens del, 700 000, kan kreves av dem privat.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
@@ -1421,9 +1421,9 @@
       </c>
       <c r="C33" s="18"/>
     </row>
-    <row r="34" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="22" t="str">
-        <f aca="false">IF(C33="JA","Hint: a: aksjekapitalen 300 000 er tapt, ingenting skyldes etterpå. b: banken mangler 700 000 og har kausjon, så den kan kreve 700 000 privat. c: 300 000 + 700 000 = 1 000 000. d: delt ansvar, 50 % av 1 400 000 = 700 000. e: solidarisk ansvar, hele 1 400 000 av hvem som helst av eierne. f: enkeltpersonforetak, hele 1 400 000.","")</f>
+        <f aca="false">IF(C33="JA","Hint: a: innskuddet 675 000 (aksjekapital 300 000 + overkurs 375 000) er tapt, ingenting skyldes etterpå. b: banken mangler 700 000 og har kausjon, så den kan kreve 700 000 privat. c: 675 000 + 700 000 = 1 375 000. d: delt ansvar, 50 % av 1 400 000 = 700 000. e: solidarisk ansvar, hele 1 400 000 av hvem som helst av eierne. f: enkeltpersonforetak, hele 1 400 000.","")</f>
         <v/>
       </c>
       <c r="C34" s="22"/>
@@ -1614,7 +1614,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="9" t="s">
         <v>47</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>63</v>
       </c>
       <c r="G21" s="17" t="str">
-        <f aca="false">IF(C21="","Skriv svaret i den gule cellen.",IF(C21=(2023),"Riktig.",IF(ABS(C21-(2022))&lt;=0,"I august 2022 hadde hun tre års praksis etter utdanningen, men elektroinstallatørprøven var ikke bestått. Det siste vilkåret avgjør.",IF(ABS(C21-(2019))&lt;=0,"Da var hun ferdig på fagskolen, men praksisen etter utdanningen manglet. Montørårene før fagskolen teller ikke.",IF(ABS(C21-(2015))&lt;=0,"Du har regnet montørårene som praksis. Praksisen skal være opparbeidet etter endt utdanning (§ 7).",IF(ABS(C21-(2020))&lt;=0,"Du har regnet montørårene med. Praksisen teller først fra august 2019, og prøven kom i 2023.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))))</f>
+        <f aca="false">IF(C21="","Skriv svaret i den gule cellen.",IF(C21=(2023),"Riktig.",IF(ABS(C21-(2022))&lt;=0,"I august 2022 hadde hun tre års praksis etter utdanningen, men elektroinstallatørprøven var ikke bestått. Det siste vilkåret avgjør.",IF(ABS(C21-(2019))&lt;=0,"Da var hun ferdig på fagskolen, men praksisen etter utdanningen manglet. Montørårene før fagskolen teller ikke.",IF(ABS(C21-(2015))&lt;=0,"Du har regnet montørårene som praksis. Praksisen skal være opparbeidet etter endt utdanning (§ 7).",IF(ABS(C21-(2020))&lt;=0,"I 2020 hadde hun bare ett års praksis etter utdanningen, og prøven var ikke bestått. For Mona er det prøven i 2023 som avgjør; montørårene teller ikke uansett.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
       <c r="Z21" s="6" t="s">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="C24" s="18"/>
       <c r="G24" s="17" t="str">
-        <f aca="false">IF(C24="","Velg i nedtrekksmenyen.",IF(C24="Ja","Riktig. § 5: faglig ansvarlig skal være fast ansatt og tilgjengelig i foretakets normale arbeidstid. Å være ute på egne oppdrag er en del av jobben.","Ikke riktig. § 5: faglig ansvarlig skal være fast ansatt og tilgjengelig i foretakets normale arbeidstid. Å være ute på egne oppdrag er en del av jobben."))</f>
+        <f aca="false">IF(C24="","Velg i nedtrekksmenyen.",IF(C24="Ja","Riktig. Kravet til faglig ansvarlig: faglig ansvarlig skal være fast ansatt og tilgjengelig i foretakets normale arbeidstid. Å være ute på egne oppdrag er en del av jobben.","Ikke riktig. Kravet til faglig ansvarlig: faglig ansvarlig skal være fast ansatt og tilgjengelig i foretakets normale arbeidstid. Å være ute på egne oppdrag er en del av jobben."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
       <c r="Z24" s="6" t="s">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C26" s="18"/>
       <c r="G26" s="17" t="str">
-        <f aca="false">IF(C26="","Velg i nedtrekksmenyen.",IF(C26="Nei","Riktig. § 3: plikten gjelder fra foretaket tilbyr arbeid. En annonse er å tilby.","Ikke riktig. § 3: plikten gjelder fra foretaket tilbyr arbeid. En annonse er å tilby."))</f>
+        <f aca="false">IF(C26="","Velg i nedtrekksmenyen.",IF(C26="Nei","Riktig. Elvirksomhetsregisteret: plikten gjelder fra foretaket tilbyr arbeid. En annonse er å tilby.","Ikke riktig. Elvirksomhetsregisteret: plikten gjelder fra foretaket tilbyr arbeid. En annonse er å tilby."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
       <c r="Z26" s="6" t="s">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="C27" s="18"/>
       <c r="G27" s="17" t="str">
-        <f aca="false">IF(C27="","Velg i nedtrekksmenyen.",IF(C27="Nei","Riktig. § 5: faglig ansvarlig kan ikke ha en stilling med sammenfallende arbeidstid i et annet foretak.","Ikke riktig. § 5: faglig ansvarlig kan ikke ha en stilling med sammenfallende arbeidstid i et annet foretak."))</f>
+        <f aca="false">IF(C27="","Velg i nedtrekksmenyen.",IF(C27="Nei","Riktig. Kravet til faglig ansvarlig: faglig ansvarlig kan ikke ha en stilling med sammenfallende arbeidstid i et annet foretak.","Ikke riktig. Kravet til faglig ansvarlig: faglig ansvarlig kan ikke ha en stilling med sammenfallende arbeidstid i et annet foretak."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="C33" s="18"/>
       <c r="G33" s="17" t="str">
-        <f aca="false">IF(C33="","Velg i nedtrekksmenyen.",IF(C33="Elvirksomhetsregisteret","Riktig. Elvirksomhetsregisteret hos Direktoratet for samfunnssikkerhet og beredskap (§ 3). Uten det kan foretaket ikke tilby elektroarbeid.","Ikke riktig. Elvirksomhetsregisteret hos Direktoratet for samfunnssikkerhet og beredskap (§ 3). Uten det kan foretaket ikke tilby elektroarbeid."))</f>
+        <f aca="false">IF(C33="","Velg i nedtrekksmenyen.",IF(C33="Elvirksomhetsregisteret","Riktig. Elvirksomhetsregisteret hos Direktoratet for samfunnssikkerhet og beredskap. Uten det kan foretaket ikke tilby elektroarbeid.","Ikke riktig. Elvirksomhetsregisteret hos Direktoratet for samfunnssikkerhet og beredskap. Uten det kan foretaket ikke tilby elektroarbeid."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
         <v>103</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>300000</v>
+        <v>675000</v>
       </c>
       <c r="D6" s="29" t="s">
         <v>104</v>
@@ -2626,7 +2626,7 @@
         <v>107</v>
       </c>
       <c r="C8" s="26" t="n">
-        <v>1000000</v>
+        <v>1375000</v>
       </c>
       <c r="D8" s="29" t="s">
         <v>108</v>
@@ -2681,7 +2681,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="29" t="s">
         <v>119</v>
       </c>

--- a/pensum/ok01/OK01_Etablering_og_oppstart_Oppgaver_v6.xlsx
+++ b/pensum/ok01/OK01_Etablering_og_oppstart_Oppgaver_v6.xlsx
@@ -648,7 +648,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -767,6 +767,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1054,7 +1058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -1079,27 +1083,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
@@ -1217,7 +1221,7 @@
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="9" t="s">
         <v>23</v>
       </c>
@@ -1235,8 +1239,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="12" t="s">
+    <row ht="31.5" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="30" r="B12" t="s">
         <v>26</v>
       </c>
       <c r="C12" s="13" t="n">
@@ -1347,7 +1351,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="25" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="14" t="s">
         <v>38</v>
       </c>
@@ -1357,7 +1361,7 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="26" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="14" t="s">
         <v>39</v>
       </c>
@@ -1645,7 +1649,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="9" t="s">
         <v>49</v>
       </c>
@@ -1781,7 +1785,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="23" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="25" t="s">
         <v>64</v>
       </c>
@@ -1853,7 +1857,7 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="30" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="25" t="s">
         <v>70</v>
       </c>
@@ -2334,7 +2338,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="22" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="14" t="s">
         <v>92</v>
       </c>
@@ -2360,7 +2364,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="60.75" customHeight="true" r="25" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="14" t="s">
         <v>94</v>
       </c>
